--- a/artfynd/A 21098-2026 artfynd.xlsx
+++ b/artfynd/A 21098-2026 artfynd.xlsx
@@ -1072,10 +1072,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>134261369</v>
+        <v>134258319</v>
       </c>
       <c r="B6" t="n">
-        <v>8460</v>
+        <v>5181</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1083,42 +1083,37 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>106545</v>
+        <v>100526</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Norra Granstorp, Norra Granstorp, Ög</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>567362</v>
+        <v>567509</v>
       </c>
       <c r="R6" t="n">
-        <v>6506686</v>
+        <v>6506789</v>
       </c>
       <c r="S6" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1174,10 +1169,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>134258319</v>
+        <v>134261369</v>
       </c>
       <c r="B7" t="n">
-        <v>5181</v>
+        <v>8460</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1185,37 +1180,42 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100526</v>
+        <v>106545</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>Norra Granstorp, Norra Granstorp, Ög</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>567509</v>
+        <v>567362</v>
       </c>
       <c r="R7" t="n">
-        <v>6506789</v>
+        <v>6506686</v>
       </c>
       <c r="S7" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1572,37 +1572,38 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>134267932</v>
+        <v>134269729</v>
       </c>
       <c r="B11" t="n">
-        <v>79978</v>
+        <v>96769</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6453</v>
+        <v>2180</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
       <c r="J11" t="inlineStr"/>
       <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr"/>
       <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
@@ -1610,10 +1611,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>567339</v>
+        <v>567745</v>
       </c>
       <c r="R11" t="n">
-        <v>6506749</v>
+        <v>6506670</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1673,39 +1674,37 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>134269975</v>
+        <v>134267932</v>
       </c>
       <c r="B12" t="n">
-        <v>8460</v>
+        <v>79978</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>106545</v>
+        <v>6453</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
       <c r="J12" t="inlineStr"/>
       <c r="K12" t="inlineStr"/>
-      <c r="L12" t="inlineStr"/>
-      <c r="M12" t="inlineStr"/>
       <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
@@ -1713,10 +1712,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>567518</v>
+        <v>567339</v>
       </c>
       <c r="R12" t="n">
-        <v>6506742</v>
+        <v>6506749</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1776,10 +1775,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>134269729</v>
+        <v>134269975</v>
       </c>
       <c r="B13" t="n">
-        <v>96769</v>
+        <v>8460</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1787,27 +1786,28 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>2180</v>
+        <v>106545</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
       <c r="J13" t="inlineStr"/>
       <c r="K13" t="inlineStr"/>
       <c r="L13" t="inlineStr"/>
+      <c r="M13" t="inlineStr"/>
       <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
@@ -1815,10 +1815,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>567745</v>
+        <v>567518</v>
       </c>
       <c r="R13" t="n">
-        <v>6506670</v>
+        <v>6506742</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2703,10 +2703,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>134260786</v>
+        <v>134270081</v>
       </c>
       <c r="B22" t="n">
-        <v>5181</v>
+        <v>106310</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2714,42 +2714,49 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>100526</v>
+        <v>221144</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr"/>
-      <c r="M22" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr"/>
+      <c r="L22" t="inlineStr"/>
+      <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Råsjön, Råsjön, Ög</t>
+          <t>Väster om Råsjön, Ög</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>567657</v>
+        <v>567413</v>
       </c>
       <c r="R22" t="n">
-        <v>6506720</v>
+        <v>6506747</v>
       </c>
       <c r="S22" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -2787,28 +2794,29 @@
       <c r="AE22" t="b">
         <v>0</v>
       </c>
+      <c r="AF22" t="inlineStr"/>
       <c r="AG22" t="b">
         <v>0</v>
       </c>
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Eva Siljeholm</t>
+          <t>Anette Källman</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Eva Siljeholm</t>
+          <t>Anette Källman</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>134270081</v>
+        <v>134260786</v>
       </c>
       <c r="B23" t="n">
-        <v>106310</v>
+        <v>5181</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2816,49 +2824,42 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>221144</v>
+        <v>100526</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>Sw.</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="J23" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K23" t="inlineStr"/>
-      <c r="L23" t="inlineStr"/>
-      <c r="N23" t="inlineStr"/>
+          <t>Paykull, 1800</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Väster om Råsjön, Ög</t>
+          <t>Råsjön, Råsjön, Ög</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>567413</v>
+        <v>567657</v>
       </c>
       <c r="R23" t="n">
-        <v>6506747</v>
+        <v>6506720</v>
       </c>
       <c r="S23" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -2896,19 +2897,18 @@
       <c r="AE23" t="b">
         <v>0</v>
       </c>
-      <c r="AF23" t="inlineStr"/>
       <c r="AG23" t="b">
         <v>0</v>
       </c>
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Anette Källman</t>
+          <t>Eva Siljeholm</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Anette Källman</t>
+          <t>Eva Siljeholm</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
@@ -3118,53 +3118,51 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>134260771</v>
+        <v>134267902</v>
       </c>
       <c r="B26" t="n">
-        <v>8460</v>
+        <v>79978</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>106545</v>
+        <v>6453</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
-      <c r="M26" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
+      <c r="J26" t="inlineStr"/>
+      <c r="K26" t="inlineStr"/>
+      <c r="N26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Råsjön, Råsjön, Ög</t>
+          <t>Väster om Råsjön, Ög</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>567657</v>
+        <v>567350</v>
       </c>
       <c r="R26" t="n">
-        <v>6506720</v>
+        <v>6506727</v>
       </c>
       <c r="S26" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3202,69 +3200,72 @@
       <c r="AE26" t="b">
         <v>0</v>
       </c>
+      <c r="AF26" t="inlineStr"/>
       <c r="AG26" t="b">
         <v>0</v>
       </c>
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Eva Siljeholm</t>
+          <t>Anette Källman</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Eva Siljeholm</t>
+          <t>Anette Källman</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>134267902</v>
+        <v>134260771</v>
       </c>
       <c r="B27" t="n">
-        <v>79978</v>
+        <v>8460</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6453</v>
+        <v>106545</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
-      <c r="J27" t="inlineStr"/>
-      <c r="K27" t="inlineStr"/>
-      <c r="N27" t="inlineStr"/>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Väster om Råsjön, Ög</t>
+          <t>Råsjön, Råsjön, Ög</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>567350</v>
+        <v>567657</v>
       </c>
       <c r="R27" t="n">
-        <v>6506727</v>
+        <v>6506720</v>
       </c>
       <c r="S27" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3302,19 +3303,18 @@
       <c r="AE27" t="b">
         <v>0</v>
       </c>
-      <c r="AF27" t="inlineStr"/>
       <c r="AG27" t="b">
         <v>0</v>
       </c>
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>Anette Källman</t>
+          <t>Eva Siljeholm</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Anette Källman</t>
+          <t>Eva Siljeholm</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>

--- a/artfynd/A 21098-2026 artfynd.xlsx
+++ b/artfynd/A 21098-2026 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>134267946</v>
       </c>
       <c r="B2" t="n">
-        <v>79978</v>
+        <v>79985</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -779,7 +779,7 @@
         <v>134268387</v>
       </c>
       <c r="B3" t="n">
-        <v>96769</v>
+        <v>96776</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -1274,7 +1274,7 @@
         <v>134260414</v>
       </c>
       <c r="B8" t="n">
-        <v>96769</v>
+        <v>96776</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1371,7 +1371,7 @@
         <v>134268127</v>
       </c>
       <c r="B9" t="n">
-        <v>96769</v>
+        <v>96776</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1473,7 +1473,7 @@
         <v>134268200</v>
       </c>
       <c r="B10" t="n">
-        <v>96769</v>
+        <v>96776</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1575,7 +1575,7 @@
         <v>134269729</v>
       </c>
       <c r="B11" t="n">
-        <v>96769</v>
+        <v>96776</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1677,7 +1677,7 @@
         <v>134267932</v>
       </c>
       <c r="B12" t="n">
-        <v>79978</v>
+        <v>79985</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1881,7 +1881,7 @@
         <v>134267891</v>
       </c>
       <c r="B14" t="n">
-        <v>79978</v>
+        <v>79985</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2092,7 +2092,7 @@
         <v>134268228</v>
       </c>
       <c r="B16" t="n">
-        <v>79978</v>
+        <v>79985</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2193,7 +2193,7 @@
         <v>134262127</v>
       </c>
       <c r="B17" t="n">
-        <v>79978</v>
+        <v>79985</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2290,7 +2290,7 @@
         <v>134259163</v>
       </c>
       <c r="B18" t="n">
-        <v>99181</v>
+        <v>99188</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2396,7 +2396,7 @@
         <v>134255123</v>
       </c>
       <c r="B19" t="n">
-        <v>79978</v>
+        <v>79985</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2493,7 +2493,7 @@
         <v>134269407</v>
       </c>
       <c r="B20" t="n">
-        <v>96769</v>
+        <v>96776</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2706,7 +2706,7 @@
         <v>134270081</v>
       </c>
       <c r="B22" t="n">
-        <v>106310</v>
+        <v>106317</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2918,7 +2918,7 @@
         <v>134269321</v>
       </c>
       <c r="B24" t="n">
-        <v>96769</v>
+        <v>96776</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3024,7 +3024,7 @@
         <v>134262232</v>
       </c>
       <c r="B25" t="n">
-        <v>96487</v>
+        <v>96494</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3121,7 +3121,7 @@
         <v>134267902</v>
       </c>
       <c r="B26" t="n">
-        <v>79978</v>
+        <v>79985</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3324,7 +3324,7 @@
         <v>134260874</v>
       </c>
       <c r="B28" t="n">
-        <v>96769</v>
+        <v>96776</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>

--- a/artfynd/A 21098-2026 artfynd.xlsx
+++ b/artfynd/A 21098-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY28"/>
+  <dimension ref="A1:AY30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,51 +675,48 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>134267946</v>
+        <v>134260414</v>
       </c>
       <c r="B2" t="n">
-        <v>79985</v>
+        <v>96783</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6453</v>
+        <v>2180</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="J2" t="inlineStr"/>
-      <c r="K2" t="inlineStr"/>
-      <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Väster om Råsjön, Ög</t>
+          <t>Råsjön, Råsjön, Ög</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>567370</v>
+        <v>567718</v>
       </c>
       <c r="R2" t="n">
-        <v>6506772</v>
+        <v>6506655</v>
       </c>
       <c r="S2" t="n">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -757,29 +754,28 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
-      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Anette Källman</t>
+          <t>Eva Siljeholm</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Anette Källman</t>
+          <t>Eva Siljeholm</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>134268387</v>
+        <v>134260874</v>
       </c>
       <c r="B3" t="n">
-        <v>96776</v>
+        <v>96783</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -805,23 +801,19 @@
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr"/>
-      <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
-      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Väster om Råsjön, Ög</t>
+          <t>Norra Granstorp, Norra Granstorp, Ög</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>567463</v>
+        <v>567614</v>
       </c>
       <c r="R3" t="n">
-        <v>6506983</v>
+        <v>6506733</v>
       </c>
       <c r="S3" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -859,29 +851,28 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
-      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Anette Källman</t>
+          <t>Eva Siljeholm</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Anette Källman</t>
+          <t>Eva Siljeholm</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>134260154</v>
+        <v>134268127</v>
       </c>
       <c r="B4" t="n">
-        <v>5181</v>
+        <v>96783</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -889,37 +880,41 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100526</v>
+        <v>2180</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr"/>
+      <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
+      <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Norra Granstorp, Norra Granstorp, Ög</t>
+          <t>Väster om Råsjön, Ög</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>567664</v>
+        <v>567408</v>
       </c>
       <c r="R4" t="n">
-        <v>6506799</v>
+        <v>6506811</v>
       </c>
       <c r="S4" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -957,28 +952,29 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
+      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Eva Siljeholm</t>
+          <t>Anette Källman</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Eva Siljeholm</t>
+          <t>Anette Källman</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>134258636</v>
+        <v>134268200</v>
       </c>
       <c r="B5" t="n">
-        <v>8460</v>
+        <v>96783</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -986,37 +982,41 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>106545</v>
+        <v>2180</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
+      <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Norra Granstorp, Norra Granstorp, Ög</t>
+          <t>Väster om Råsjön, Ög</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>567528</v>
+        <v>567398</v>
       </c>
       <c r="R5" t="n">
-        <v>6506757</v>
+        <v>6506814</v>
       </c>
       <c r="S5" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1054,28 +1054,29 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
+      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Eva Siljeholm</t>
+          <t>Anette Källman</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Eva Siljeholm</t>
+          <t>Anette Källman</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>134258319</v>
+        <v>134268387</v>
       </c>
       <c r="B6" t="n">
-        <v>5181</v>
+        <v>96783</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1083,37 +1084,41 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100526</v>
+        <v>2180</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
+      <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Norra Granstorp, Norra Granstorp, Ög</t>
+          <t>Väster om Råsjön, Ög</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>567509</v>
+        <v>567463</v>
       </c>
       <c r="R6" t="n">
-        <v>6506789</v>
+        <v>6506983</v>
       </c>
       <c r="S6" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1151,28 +1156,29 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
+      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Eva Siljeholm</t>
+          <t>Anette Källman</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Eva Siljeholm</t>
+          <t>Anette Källman</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>134261369</v>
+        <v>134269321</v>
       </c>
       <c r="B7" t="n">
-        <v>8460</v>
+        <v>96783</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1180,42 +1186,41 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>106545</v>
+        <v>2180</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
+      <c r="J7" t="inlineStr"/>
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
+      <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Norra Granstorp, Norra Granstorp, Ög</t>
+          <t>Väster om Råsjön, Ög</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>567362</v>
+        <v>567609</v>
       </c>
       <c r="R7" t="n">
-        <v>6506686</v>
+        <v>6506814</v>
       </c>
       <c r="S7" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1253,28 +1258,33 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
+      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Eva Siljeholm</t>
+          <t>Anette Källman</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Eva Siljeholm</t>
-        </is>
-      </c>
-      <c r="AY7" t="inlineStr"/>
+          <t>Anette Källman</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr">
+        <is>
+          <t>Skyddsvärda träd</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>134260414</v>
+        <v>134269407</v>
       </c>
       <c r="B8" t="n">
-        <v>96776</v>
+        <v>96783</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1300,19 +1310,23 @@
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr"/>
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
+      <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Råsjön, Råsjön, Ög</t>
+          <t>Väster om Råsjön, Ög</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>567718</v>
+        <v>567618</v>
       </c>
       <c r="R8" t="n">
-        <v>6506655</v>
+        <v>6506890</v>
       </c>
       <c r="S8" t="n">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1350,28 +1364,33 @@
       <c r="AE8" t="b">
         <v>0</v>
       </c>
+      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Eva Siljeholm</t>
+          <t>Anette Källman</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Eva Siljeholm</t>
-        </is>
-      </c>
-      <c r="AY8" t="inlineStr"/>
+          <t>Anette Källman</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr">
+        <is>
+          <t>Skyddsvärda träd</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>134268127</v>
+        <v>134269729</v>
       </c>
       <c r="B9" t="n">
-        <v>96776</v>
+        <v>96783</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1407,10 +1426,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>567408</v>
+        <v>567745</v>
       </c>
       <c r="R9" t="n">
-        <v>6506811</v>
+        <v>6506670</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1470,10 +1489,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>134268200</v>
+        <v>134262232</v>
       </c>
       <c r="B10" t="n">
-        <v>96776</v>
+        <v>96501</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1481,41 +1500,37 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>2180</v>
+        <v>2671</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Fällmossa</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Antitrichia curtipendula</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>(Hedw.) Brid.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="J10" t="inlineStr"/>
-      <c r="K10" t="inlineStr"/>
-      <c r="L10" t="inlineStr"/>
-      <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Väster om Råsjön, Ög</t>
+          <t>Norra Granstorp, Norra Granstorp, Ög</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>567398</v>
+        <v>567280</v>
       </c>
       <c r="R10" t="n">
-        <v>6506814</v>
+        <v>6506816</v>
       </c>
       <c r="S10" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1553,71 +1568,66 @@
       <c r="AE10" t="b">
         <v>0</v>
       </c>
-      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
       </c>
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Anette Källman</t>
+          <t>Eva Siljeholm</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Anette Källman</t>
+          <t>Eva Siljeholm</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>134269729</v>
+        <v>134255011</v>
       </c>
       <c r="B11" t="n">
-        <v>96776</v>
+        <v>79992</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>2180</v>
+        <v>6453</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
-      <c r="J11" t="inlineStr"/>
-      <c r="K11" t="inlineStr"/>
-      <c r="L11" t="inlineStr"/>
-      <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Väster om Råsjön, Ög</t>
+          <t>Norra Granstorp, Norra Granstorp, Ög</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>567745</v>
+        <v>567338</v>
       </c>
       <c r="R11" t="n">
-        <v>6506670</v>
+        <v>6506695</v>
       </c>
       <c r="S11" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1655,29 +1665,28 @@
       <c r="AE11" t="b">
         <v>0</v>
       </c>
-      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Anette Källman</t>
+          <t>Eva Siljeholm</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Anette Källman</t>
+          <t>Eva Siljeholm</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>134267932</v>
+        <v>134255123</v>
       </c>
       <c r="B12" t="n">
-        <v>79985</v>
+        <v>79992</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1703,22 +1712,19 @@
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
-      <c r="J12" t="inlineStr"/>
-      <c r="K12" t="inlineStr"/>
-      <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Väster om Råsjön, Ög</t>
+          <t>Norra Granstorp, Norra Granstorp, Ög</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>567339</v>
+        <v>567343</v>
       </c>
       <c r="R12" t="n">
-        <v>6506749</v>
+        <v>6506722</v>
       </c>
       <c r="S12" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1756,72 +1762,66 @@
       <c r="AE12" t="b">
         <v>0</v>
       </c>
-      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
       </c>
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Anette Källman</t>
+          <t>Eva Siljeholm</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Anette Källman</t>
+          <t>Eva Siljeholm</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>134269975</v>
+        <v>134262127</v>
       </c>
       <c r="B13" t="n">
-        <v>8460</v>
+        <v>79992</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>106545</v>
+        <v>6453</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
-      <c r="J13" t="inlineStr"/>
-      <c r="K13" t="inlineStr"/>
-      <c r="L13" t="inlineStr"/>
-      <c r="M13" t="inlineStr"/>
-      <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Väster om Råsjön, Ög</t>
+          <t>Norra Granstorp, Norra Granstorp, Ög</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>567518</v>
+        <v>567280</v>
       </c>
       <c r="R13" t="n">
-        <v>6506742</v>
+        <v>6506816</v>
       </c>
       <c r="S13" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1859,19 +1859,18 @@
       <c r="AE13" t="b">
         <v>0</v>
       </c>
-      <c r="AF13" t="inlineStr"/>
       <c r="AG13" t="b">
         <v>0</v>
       </c>
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Anette Källman</t>
+          <t>Eva Siljeholm</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Anette Källman</t>
+          <t>Eva Siljeholm</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
@@ -1881,7 +1880,7 @@
         <v>134267891</v>
       </c>
       <c r="B14" t="n">
-        <v>79985</v>
+        <v>79992</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1979,10 +1978,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>134269835</v>
+        <v>134267902</v>
       </c>
       <c r="B15" t="n">
-        <v>57972</v>
+        <v>79992</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -1990,31 +1989,26 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100049</v>
+        <v>6453</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
+      <c r="J15" t="inlineStr"/>
       <c r="K15" t="inlineStr"/>
-      <c r="L15" t="inlineStr"/>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
@@ -2022,10 +2016,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>567703</v>
+        <v>567350</v>
       </c>
       <c r="R15" t="n">
-        <v>6506653</v>
+        <v>6506727</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2060,17 +2054,13 @@
           <t>2026-06-09</t>
         </is>
       </c>
-      <c r="AC15" t="inlineStr">
-        <is>
-          <t>Födosök i tallraka</t>
-        </is>
-      </c>
       <c r="AD15" t="b">
         <v>0</v>
       </c>
       <c r="AE15" t="b">
         <v>0</v>
       </c>
+      <c r="AF15" t="inlineStr"/>
       <c r="AG15" t="b">
         <v>0</v>
       </c>
@@ -2089,10 +2079,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>134268228</v>
+        <v>134267932</v>
       </c>
       <c r="B16" t="n">
-        <v>79985</v>
+        <v>79992</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2127,10 +2117,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>567370</v>
+        <v>567339</v>
       </c>
       <c r="R16" t="n">
-        <v>6506874</v>
+        <v>6506749</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2190,10 +2180,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>134262127</v>
+        <v>134267946</v>
       </c>
       <c r="B17" t="n">
-        <v>79985</v>
+        <v>79992</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2219,19 +2209,22 @@
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
+      <c r="J17" t="inlineStr"/>
+      <c r="K17" t="inlineStr"/>
+      <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Norra Granstorp, Norra Granstorp, Ög</t>
+          <t>Väster om Råsjön, Ög</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>567280</v>
+        <v>567370</v>
       </c>
       <c r="R17" t="n">
-        <v>6506816</v>
+        <v>6506772</v>
       </c>
       <c r="S17" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2269,75 +2262,70 @@
       <c r="AE17" t="b">
         <v>0</v>
       </c>
+      <c r="AF17" t="inlineStr"/>
       <c r="AG17" t="b">
         <v>0</v>
       </c>
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Eva Siljeholm</t>
+          <t>Anette Källman</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Eva Siljeholm</t>
+          <t>Anette Källman</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>134259163</v>
+        <v>134268228</v>
       </c>
       <c r="B18" t="n">
-        <v>99188</v>
+        <v>79992</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>220787</v>
+        <v>6453</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>120</t>
-        </is>
-      </c>
-      <c r="J18" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
+      <c r="J18" t="inlineStr"/>
+      <c r="K18" t="inlineStr"/>
+      <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Norra Granstorp, Norra Granstorp, Ög</t>
+          <t>Väster om Råsjön, Ög</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>567559</v>
+        <v>567370</v>
       </c>
       <c r="R18" t="n">
-        <v>6506759</v>
+        <v>6506874</v>
       </c>
       <c r="S18" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2375,66 +2363,75 @@
       <c r="AE18" t="b">
         <v>0</v>
       </c>
+      <c r="AF18" t="inlineStr"/>
       <c r="AG18" t="b">
         <v>0</v>
       </c>
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Eva Siljeholm</t>
+          <t>Anette Källman</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Eva Siljeholm</t>
+          <t>Anette Källman</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>134255123</v>
+        <v>134269835</v>
       </c>
       <c r="B19" t="n">
-        <v>79985</v>
+        <v>57972</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6453</v>
+        <v>100049</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
+      <c r="K19" t="inlineStr"/>
+      <c r="L19" t="inlineStr"/>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Norra Granstorp, Norra Granstorp, Ög</t>
+          <t>Väster om Råsjön, Ög</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>567343</v>
+        <v>567703</v>
       </c>
       <c r="R19" t="n">
-        <v>6506722</v>
+        <v>6506653</v>
       </c>
       <c r="S19" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2464,6 +2461,11 @@
       <c r="AA19" t="inlineStr">
         <is>
           <t>2026-06-09</t>
+        </is>
+      </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>Födosök i tallraka</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2478,22 +2480,22 @@
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Eva Siljeholm</t>
+          <t>Anette Källman</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Eva Siljeholm</t>
+          <t>Anette Källman</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>134269407</v>
+        <v>134258319</v>
       </c>
       <c r="B20" t="n">
-        <v>96776</v>
+        <v>5181</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2501,41 +2503,37 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>2180</v>
+        <v>100526</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
-      <c r="J20" t="inlineStr"/>
-      <c r="K20" t="inlineStr"/>
-      <c r="L20" t="inlineStr"/>
-      <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Väster om Råsjön, Ög</t>
+          <t>Norra Granstorp, Norra Granstorp, Ög</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>567618</v>
+        <v>567509</v>
       </c>
       <c r="R20" t="n">
-        <v>6506890</v>
+        <v>6506789</v>
       </c>
       <c r="S20" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2573,33 +2571,28 @@
       <c r="AE20" t="b">
         <v>0</v>
       </c>
-      <c r="AF20" t="inlineStr"/>
       <c r="AG20" t="b">
         <v>0</v>
       </c>
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Anette Källman</t>
+          <t>Eva Siljeholm</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Anette Källman</t>
-        </is>
-      </c>
-      <c r="AY20" t="inlineStr">
-        <is>
-          <t>Skyddsvärda träd</t>
-        </is>
-      </c>
+          <t>Eva Siljeholm</t>
+        </is>
+      </c>
+      <c r="AY20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>134269263</v>
+        <v>134260154</v>
       </c>
       <c r="B21" t="n">
-        <v>8460</v>
+        <v>5181</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2607,42 +2600,37 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>106545</v>
+        <v>100526</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
-      <c r="J21" t="inlineStr"/>
-      <c r="K21" t="inlineStr"/>
-      <c r="L21" t="inlineStr"/>
-      <c r="M21" t="inlineStr"/>
-      <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Väster om Råsjön, Ög</t>
+          <t>Norra Granstorp, Norra Granstorp, Ög</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>567537</v>
+        <v>567664</v>
       </c>
       <c r="R21" t="n">
-        <v>6506745</v>
+        <v>6506799</v>
       </c>
       <c r="S21" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -2680,33 +2668,28 @@
       <c r="AE21" t="b">
         <v>0</v>
       </c>
-      <c r="AF21" t="inlineStr"/>
       <c r="AG21" t="b">
         <v>0</v>
       </c>
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Anette Källman</t>
+          <t>Eva Siljeholm</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Anette Källman</t>
-        </is>
-      </c>
-      <c r="AY21" t="inlineStr">
-        <is>
-          <t>Skyddsvärda träd</t>
-        </is>
-      </c>
+          <t>Eva Siljeholm</t>
+        </is>
+      </c>
+      <c r="AY21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>134270081</v>
+        <v>134260786</v>
       </c>
       <c r="B22" t="n">
-        <v>106317</v>
+        <v>5181</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2714,49 +2697,42 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>221144</v>
+        <v>100526</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>Sw.</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="J22" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K22" t="inlineStr"/>
-      <c r="L22" t="inlineStr"/>
-      <c r="N22" t="inlineStr"/>
+          <t>Paykull, 1800</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Väster om Råsjön, Ög</t>
+          <t>Råsjön, Råsjön, Ög</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>567413</v>
+        <v>567657</v>
       </c>
       <c r="R22" t="n">
-        <v>6506747</v>
+        <v>6506720</v>
       </c>
       <c r="S22" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -2794,29 +2770,28 @@
       <c r="AE22" t="b">
         <v>0</v>
       </c>
-      <c r="AF22" t="inlineStr"/>
       <c r="AG22" t="b">
         <v>0</v>
       </c>
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Anette Källman</t>
+          <t>Eva Siljeholm</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Anette Källman</t>
+          <t>Eva Siljeholm</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>134260786</v>
+        <v>134258636</v>
       </c>
       <c r="B23" t="n">
-        <v>5181</v>
+        <v>8460</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2824,42 +2799,37 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>100526</v>
+        <v>106545</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
-      <c r="M23" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Råsjön, Råsjön, Ög</t>
+          <t>Norra Granstorp, Norra Granstorp, Ög</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>567657</v>
+        <v>567528</v>
       </c>
       <c r="R23" t="n">
-        <v>6506720</v>
+        <v>6506757</v>
       </c>
       <c r="S23" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -2915,10 +2885,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>134269321</v>
+        <v>134260771</v>
       </c>
       <c r="B24" t="n">
-        <v>96776</v>
+        <v>8460</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2926,41 +2896,42 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>2180</v>
+        <v>106545</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
-      <c r="J24" t="inlineStr"/>
-      <c r="K24" t="inlineStr"/>
-      <c r="L24" t="inlineStr"/>
-      <c r="N24" t="inlineStr"/>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Väster om Råsjön, Ög</t>
+          <t>Råsjön, Råsjön, Ög</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>567609</v>
+        <v>567657</v>
       </c>
       <c r="R24" t="n">
-        <v>6506814</v>
+        <v>6506720</v>
       </c>
       <c r="S24" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -2998,33 +2969,28 @@
       <c r="AE24" t="b">
         <v>0</v>
       </c>
-      <c r="AF24" t="inlineStr"/>
       <c r="AG24" t="b">
         <v>0</v>
       </c>
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Anette Källman</t>
+          <t>Eva Siljeholm</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Anette Källman</t>
-        </is>
-      </c>
-      <c r="AY24" t="inlineStr">
-        <is>
-          <t>Skyddsvärda träd</t>
-        </is>
-      </c>
+          <t>Eva Siljeholm</t>
+        </is>
+      </c>
+      <c r="AY24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>134262232</v>
+        <v>134261369</v>
       </c>
       <c r="B25" t="n">
-        <v>96494</v>
+        <v>8460</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3032,37 +2998,42 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>2671</v>
+        <v>106545</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Fällmossa</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Antitrichia curtipendula</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Hedw.) Brid.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P25" t="inlineStr">
         <is>
           <t>Norra Granstorp, Norra Granstorp, Ög</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>567280</v>
+        <v>567362</v>
       </c>
       <c r="R25" t="n">
-        <v>6506816</v>
+        <v>6506686</v>
       </c>
       <c r="S25" t="n">
-        <v>4</v>
+        <v>25</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3118,37 +3089,39 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>134267902</v>
+        <v>134269263</v>
       </c>
       <c r="B26" t="n">
-        <v>79985</v>
+        <v>8460</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6453</v>
+        <v>106545</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
       <c r="J26" t="inlineStr"/>
       <c r="K26" t="inlineStr"/>
+      <c r="L26" t="inlineStr"/>
+      <c r="M26" t="inlineStr"/>
       <c r="N26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
@@ -3156,10 +3129,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>567350</v>
+        <v>567537</v>
       </c>
       <c r="R26" t="n">
-        <v>6506727</v>
+        <v>6506745</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3215,11 +3188,15 @@
           <t>Anette Källman</t>
         </is>
       </c>
-      <c r="AY26" t="inlineStr"/>
+      <c r="AY26" t="inlineStr">
+        <is>
+          <t>Skyddsvärda träd</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>134260771</v>
+        <v>134269975</v>
       </c>
       <c r="B27" t="n">
         <v>8460</v>
@@ -3248,24 +3225,24 @@
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
-      <c r="M27" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
+      <c r="J27" t="inlineStr"/>
+      <c r="K27" t="inlineStr"/>
+      <c r="L27" t="inlineStr"/>
+      <c r="M27" t="inlineStr"/>
+      <c r="N27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Råsjön, Råsjön, Ög</t>
+          <t>Väster om Råsjön, Ög</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>567657</v>
+        <v>567518</v>
       </c>
       <c r="R27" t="n">
-        <v>6506720</v>
+        <v>6506742</v>
       </c>
       <c r="S27" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3303,63 +3280,73 @@
       <c r="AE27" t="b">
         <v>0</v>
       </c>
+      <c r="AF27" t="inlineStr"/>
       <c r="AG27" t="b">
         <v>0</v>
       </c>
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>Eva Siljeholm</t>
+          <t>Anette Källman</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Eva Siljeholm</t>
+          <t>Anette Källman</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>134260874</v>
+        <v>134259163</v>
       </c>
       <c r="B28" t="n">
-        <v>96776</v>
+        <v>99195</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>2180</v>
+        <v>220787</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
-        </is>
-      </c>
-      <c r="I28" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>120</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P28" t="inlineStr">
         <is>
           <t>Norra Granstorp, Norra Granstorp, Ög</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>567614</v>
+        <v>567559</v>
       </c>
       <c r="R28" t="n">
-        <v>6506733</v>
+        <v>6506759</v>
       </c>
       <c r="S28" t="n">
         <v>4</v>
@@ -3415,6 +3402,213 @@
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>134270081</v>
+      </c>
+      <c r="B29" t="n">
+        <v>106324</v>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E29" t="n">
+        <v>221144</v>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>Grönpyrola</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>Pyrola chlorantha</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K29" t="inlineStr"/>
+      <c r="L29" t="inlineStr"/>
+      <c r="N29" t="inlineStr"/>
+      <c r="P29" t="inlineStr">
+        <is>
+          <t>Väster om Råsjön, Ög</t>
+        </is>
+      </c>
+      <c r="Q29" t="n">
+        <v>567413</v>
+      </c>
+      <c r="R29" t="n">
+        <v>6506747</v>
+      </c>
+      <c r="S29" t="n">
+        <v>10</v>
+      </c>
+      <c r="T29" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U29" t="inlineStr">
+        <is>
+          <t>Norrköping</t>
+        </is>
+      </c>
+      <c r="V29" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W29" t="inlineStr">
+        <is>
+          <t>Kvillinge</t>
+        </is>
+      </c>
+      <c r="Y29" t="inlineStr">
+        <is>
+          <t>2026-06-09</t>
+        </is>
+      </c>
+      <c r="AA29" t="inlineStr">
+        <is>
+          <t>2026-06-09</t>
+        </is>
+      </c>
+      <c r="AD29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF29" t="inlineStr"/>
+      <c r="AG29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT29" t="inlineStr"/>
+      <c r="AW29" t="inlineStr">
+        <is>
+          <t>Anette Källman</t>
+        </is>
+      </c>
+      <c r="AX29" t="inlineStr">
+        <is>
+          <t>Anette Källman</t>
+        </is>
+      </c>
+      <c r="AY29" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>134258415</v>
+      </c>
+      <c r="B30" t="n">
+        <v>99960</v>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E30" t="n">
+        <v>222364</v>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>Skärmstarr</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>Carex remota</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr"/>
+      <c r="P30" t="inlineStr">
+        <is>
+          <t>Norra Granstorp, Norra Granstorp, Ög</t>
+        </is>
+      </c>
+      <c r="Q30" t="n">
+        <v>567509</v>
+      </c>
+      <c r="R30" t="n">
+        <v>6506789</v>
+      </c>
+      <c r="S30" t="n">
+        <v>20</v>
+      </c>
+      <c r="T30" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U30" t="inlineStr">
+        <is>
+          <t>Norrköping</t>
+        </is>
+      </c>
+      <c r="V30" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W30" t="inlineStr">
+        <is>
+          <t>Kvillinge</t>
+        </is>
+      </c>
+      <c r="Y30" t="inlineStr">
+        <is>
+          <t>2026-06-09</t>
+        </is>
+      </c>
+      <c r="AA30" t="inlineStr">
+        <is>
+          <t>2026-06-09</t>
+        </is>
+      </c>
+      <c r="AD30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT30" t="inlineStr"/>
+      <c r="AW30" t="inlineStr">
+        <is>
+          <t>Eva Siljeholm</t>
+        </is>
+      </c>
+      <c r="AX30" t="inlineStr">
+        <is>
+          <t>Eva Siljeholm</t>
+        </is>
+      </c>
+      <c r="AY30" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 21098-2026 artfynd.xlsx
+++ b/artfynd/A 21098-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY30"/>
+  <dimension ref="A1:AZ30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -769,6 +774,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134260414</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -866,6 +876,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134260874</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -968,6 +983,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134268127</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1070,6 +1090,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134268200</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1172,6 +1197,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134268387</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1278,6 +1308,11 @@
           <t>Skyddsvärda träd</t>
         </is>
       </c>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134269321</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1384,6 +1419,11 @@
           <t>Skyddsvärda träd</t>
         </is>
       </c>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134269407</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1486,6 +1526,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134269729</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1583,6 +1628,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134262232</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1680,6 +1730,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134255011</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1777,6 +1832,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134255123</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1874,6 +1934,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134262127</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -1975,6 +2040,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134267891</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2076,6 +2146,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134267902</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2177,6 +2252,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134267932</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2278,6 +2358,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134267946</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2379,6 +2464,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134268228</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2489,6 +2579,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134269835</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2586,6 +2681,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134258319</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2683,6 +2783,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134260154</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2785,6 +2890,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134260786</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -2882,6 +2992,11 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134258636</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -2984,6 +3099,11 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134260771</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3086,6 +3206,11 @@
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134261369</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3193,6 +3318,11 @@
           <t>Skyddsvärda träd</t>
         </is>
       </c>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134269263</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3296,6 +3426,11 @@
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134269975</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -3402,6 +3537,11 @@
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134259163</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -3512,6 +3652,11 @@
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134270081</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -3609,8 +3754,44 @@
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134258415</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>